--- a/public/exports-with-coowners/32264328.xlsx
+++ b/public/exports-with-coowners/32264328.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t xml:space="preserve">311221240</t>
+          <t xml:space="preserve">311221242</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t xml:space="preserve">311221240</t>
+          <t xml:space="preserve">311221242</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t xml:space="preserve">311221240</t>
+          <t xml:space="preserve">311221242</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">

--- a/public/exports-with-coowners/32264328.xlsx
+++ b/public/exports-with-coowners/32264328.xlsx
@@ -116,7 +116,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alrøvej 357</t>
+          <t xml:space="preserve">Havnegade 4B</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -126,16 +126,16 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4191418</t>
+          <t xml:space="preserve">4194186</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J2">
-        <v>417</v>
+        <v>266</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -191,7 +191,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnegade 4B</t>
+          <t xml:space="preserve">Højmarkvej 10</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -201,16 +201,16 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4194186</t>
+          <t xml:space="preserve">4197392</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J3">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -266,26 +266,26 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højmarkvej 10</t>
+          <t xml:space="preserve">Landevejen 30</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">8300</t>
+          <t xml:space="preserve">8350</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4197392</t>
+          <t xml:space="preserve">4194793</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J4">
-        <v>257</v>
+        <v>1607</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -341,26 +341,26 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Landevejen 30</t>
+          <t xml:space="preserve">Møllevej 3</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">8350</t>
+          <t xml:space="preserve">8300</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">4194793</t>
+          <t xml:space="preserve">4199045</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J5">
-        <v>1607</v>
+        <v>500</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -416,7 +416,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllevej 3</t>
+          <t xml:space="preserve">Nølevvej 6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -426,16 +426,16 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">4199045</t>
+          <t xml:space="preserve">7349415</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="J6">
-        <v>500</v>
+        <v>3084</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -491,7 +491,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nølevvej 6</t>
+          <t xml:space="preserve">Skolegade 65</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -501,16 +501,16 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">7349415</t>
+          <t xml:space="preserve">8567114, 100197236</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J7">
-        <v>3084</v>
+        <v>2273</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -551,12 +551,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Odder Kommune</t>
+          <t xml:space="preserve">S/I Den selvejende almene OK-plejeboliginstitution i Stenslund</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 65</t>
+          <t xml:space="preserve">Stenslund 4</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8567114, 100197236</t>
+          <t xml:space="preserve">100275815, 100275816</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="J8">
-        <v>2273</v>
+        <v>2046</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -626,12 +626,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">S/I Den selvejende almene OK-plejeboliginstitution i Stenslund</t>
+          <t xml:space="preserve">Odder Kommune</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stenslund 4</t>
+          <t xml:space="preserve">Stenslund 7</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -651,16 +651,16 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">100275815, 100275816</t>
+          <t xml:space="preserve">8097328</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J9">
-        <v>2046</v>
+        <v>312</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -731,11 +731,11 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J10">
-        <v>312</v>
+        <v>251</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -791,26 +791,26 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stenslund 7</t>
+          <t xml:space="preserve">Tunø Hovedgade 10</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">8300</t>
+          <t xml:space="preserve">8799</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">8097328</t>
+          <t xml:space="preserve">4248229</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J11">
-        <v>251</v>
+        <v>421</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -866,26 +866,26 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tunø Hovedgade 10</t>
+          <t xml:space="preserve">Vitavej 60</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">8799</t>
+          <t xml:space="preserve">8300</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">4248229</t>
+          <t xml:space="preserve">4196608</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J12">
-        <v>421</v>
+        <v>629</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vennelundsvej 95</t>
+          <t xml:space="preserve">Holsteinsgade 43A</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -951,35 +951,35 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">8375804</t>
+          <t xml:space="preserve">4199447</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J13">
-        <v>994</v>
+        <v>759</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200026991</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Rambøll Danmark A/S (Ålborg)</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2020-01-19</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1016,7 +1016,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vennelundsvej 95</t>
+          <t xml:space="preserve">Egholmvej 2</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1026,35 +1026,35 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">8375804</t>
+          <t xml:space="preserve">4197672</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J14">
-        <v>2372</v>
+        <v>512</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311203242</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2026-09-28</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vitavej 60</t>
+          <t xml:space="preserve">Egholmvej 6</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1101,35 +1101,35 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">4196608</t>
+          <t xml:space="preserve">4197674</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J15">
-        <v>629</v>
+        <v>276</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311203232</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2026-09-28</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holsteinsgade 43A</t>
+          <t xml:space="preserve">Egholmvej 6</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">4199447</t>
+          <t xml:space="preserve">4197674</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1185,21 +1185,21 @@
         </is>
       </c>
       <c r="J16">
-        <v>759</v>
+        <v>282</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t xml:space="preserve">200026991</t>
+          <t xml:space="preserve">311203232</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S (Ålborg)</t>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-01-19</t>
+          <t xml:space="preserve">2026-09-28</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aahavevej 10</t>
+          <t xml:space="preserve">Egholmvej 6</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1251,20 +1251,20 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">4197460</t>
+          <t xml:space="preserve">4197674</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J17">
-        <v>253</v>
+        <v>294</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t xml:space="preserve">311203234</t>
+          <t xml:space="preserve">311203232</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1279,12 +1279,12 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egholmvej 2</t>
+          <t xml:space="preserve">Egholmvej 6</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1326,20 +1326,20 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">4197672</t>
+          <t xml:space="preserve">4197674</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J18">
-        <v>512</v>
+        <v>499</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t xml:space="preserve">311203242</t>
+          <t xml:space="preserve">311203232</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egholmvej 6</t>
+          <t xml:space="preserve">Bronzealdervej 16</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1406,15 +1406,15 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J19">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t xml:space="preserve">311203232</t>
+          <t xml:space="preserve">311208182</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-28</t>
+          <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egholmvej 6</t>
+          <t xml:space="preserve">Saloparken 2</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1476,20 +1476,20 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">4197674</t>
+          <t xml:space="preserve">7255382</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J20">
-        <v>282</v>
+        <v>555</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t xml:space="preserve">311203232</t>
+          <t xml:space="preserve">311208186</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-28</t>
+          <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egholmvej 6</t>
+          <t xml:space="preserve">Torvald Køhlsvej 50</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1551,20 +1551,20 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">4197674</t>
+          <t xml:space="preserve">9665232</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J21">
-        <v>294</v>
+        <v>398</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t xml:space="preserve">311203232</t>
+          <t xml:space="preserve">311208185</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-28</t>
+          <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egholmvej 6</t>
+          <t xml:space="preserve">Skolegade 15A</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1626,20 +1626,20 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">4197674</t>
+          <t xml:space="preserve">4193708</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J22">
-        <v>499</v>
+        <v>398</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t xml:space="preserve">311203232</t>
+          <t xml:space="preserve">311218214</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-28</t>
+          <t xml:space="preserve">2026-12-16</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bronzealdervej 16</t>
+          <t xml:space="preserve">Venneslaparken 1</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1701,20 +1701,20 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">4197674</t>
+          <t xml:space="preserve">7956622</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J23">
-        <v>270</v>
+        <v>480</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t xml:space="preserve">311208182</t>
+          <t xml:space="preserve">311218471</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-24</t>
+          <t xml:space="preserve">2026-12-19</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -1766,17 +1766,17 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Saloparken 2</t>
+          <t xml:space="preserve">Landevejen 30</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">8300</t>
+          <t xml:space="preserve">8350</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">7255382</t>
+          <t xml:space="preserve">4194779</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1785,11 +1785,11 @@
         </is>
       </c>
       <c r="J24">
-        <v>555</v>
+        <v>275</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t xml:space="preserve">311208186</t>
+          <t xml:space="preserve">311221278</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-24</t>
+          <t xml:space="preserve">2027-01-06</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Torvald Køhlsvej 50</t>
+          <t xml:space="preserve">Rudevej 100</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">9665232</t>
+          <t xml:space="preserve">9995805</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1860,11 +1860,11 @@
         </is>
       </c>
       <c r="J25">
-        <v>398</v>
+        <v>894</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t xml:space="preserve">311208185</t>
+          <t xml:space="preserve">311221242</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-24</t>
+          <t xml:space="preserve">2027-01-06</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -1916,7 +1916,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gylling Skolegade 12</t>
+          <t xml:space="preserve">Rudevej 100</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1926,20 +1926,20 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">4193329</t>
+          <t xml:space="preserve">9995805</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J26">
-        <v>442</v>
+        <v>329</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t xml:space="preserve">311211745</t>
+          <t xml:space="preserve">311221242</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-11</t>
+          <t xml:space="preserve">2027-01-06</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 15A</t>
+          <t xml:space="preserve">Rudevej 100</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2001,20 +2001,20 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">4193708</t>
+          <t xml:space="preserve">9995805</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J27">
-        <v>398</v>
+        <v>428</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t xml:space="preserve">311218214</t>
+          <t xml:space="preserve">311221242</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-16</t>
+          <t xml:space="preserve">2027-01-06</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Venneslaparken 1</t>
+          <t xml:space="preserve">Rudevej 100</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2076,20 +2076,20 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">7956622</t>
+          <t xml:space="preserve">9995805</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J28">
-        <v>480</v>
+        <v>1621</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t xml:space="preserve">311218471</t>
+          <t xml:space="preserve">311221242</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-19</t>
+          <t xml:space="preserve">2027-01-06</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2141,17 +2141,17 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Landevejen 30</t>
+          <t xml:space="preserve">Østermarksvej 25A</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">8350</t>
+          <t xml:space="preserve">8300</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">4194779</t>
+          <t xml:space="preserve">100049247</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2160,21 +2160,21 @@
         </is>
       </c>
       <c r="J29">
-        <v>275</v>
+        <v>620</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t xml:space="preserve">311221278</t>
+          <t xml:space="preserve">311224995</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">Bornak Arkitekter</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-06</t>
+          <t xml:space="preserve">2027-01-27</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rudevej 100</t>
+          <t xml:space="preserve">Nølevvej 4</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">9995805</t>
+          <t xml:space="preserve">7349419</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2235,11 +2235,11 @@
         </is>
       </c>
       <c r="J30">
-        <v>894</v>
+        <v>11918</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t xml:space="preserve">311221242</t>
+          <t xml:space="preserve">311230441</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-06</t>
+          <t xml:space="preserve">2027-02-24</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rudevej 100</t>
+          <t xml:space="preserve">Mejerivej 14</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2301,20 +2301,20 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">9995805</t>
+          <t xml:space="preserve">4196620</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J31">
-        <v>329</v>
+        <v>887</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t xml:space="preserve">311221242</t>
+          <t xml:space="preserve">311253199</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-06</t>
+          <t xml:space="preserve">2027-06-12</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rudevej 100</t>
+          <t xml:space="preserve">Bronzealdervej 10</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2376,20 +2376,20 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">9995805</t>
+          <t xml:space="preserve">100052507</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J32">
-        <v>428</v>
+        <v>787</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t xml:space="preserve">311221242</t>
+          <t xml:space="preserve">311258871</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2399,7 +2399,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-06</t>
+          <t xml:space="preserve">2027-07-04</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rudevej 100</t>
+          <t xml:space="preserve">Bronzealdervej 12</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2451,20 +2451,20 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">9995805</t>
+          <t xml:space="preserve">100052507</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J33">
-        <v>1621</v>
+        <v>787</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t xml:space="preserve">311221242</t>
+          <t xml:space="preserve">311258871</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-06</t>
+          <t xml:space="preserve">2027-07-04</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevænget 1</t>
+          <t xml:space="preserve">Bronzealdervej 14</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2526,20 +2526,20 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">4193843</t>
+          <t xml:space="preserve">100052507</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J34">
-        <v>3079</v>
+        <v>787</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t xml:space="preserve">311221268</t>
+          <t xml:space="preserve">311258871</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-06</t>
+          <t xml:space="preserve">2027-07-04</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevænget 1</t>
+          <t xml:space="preserve">Bronzealdervej 2</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2601,20 +2601,20 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">4193843</t>
+          <t xml:space="preserve">100052507</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J35">
-        <v>695</v>
+        <v>787</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t xml:space="preserve">311221268</t>
+          <t xml:space="preserve">311258871</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-06</t>
+          <t xml:space="preserve">2027-07-04</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østermarksvej 25A</t>
+          <t xml:space="preserve">Bronzealdervej 4</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2676,30 +2676,30 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">100049247</t>
+          <t xml:space="preserve">100052507</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J36">
-        <v>620</v>
+        <v>787</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t xml:space="preserve">311224995</t>
+          <t xml:space="preserve">311258871</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bornak Arkitekter</t>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-27</t>
+          <t xml:space="preserve">2027-07-04</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gylling Skolegade 13</t>
+          <t xml:space="preserve">Bronzealdervej 6</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2751,20 +2751,20 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">4193434</t>
+          <t xml:space="preserve">100052507</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J37">
-        <v>2202</v>
+        <v>787</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t xml:space="preserve">311230442</t>
+          <t xml:space="preserve">311258871</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-24</t>
+          <t xml:space="preserve">2027-07-04</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nølevvej 4</t>
+          <t xml:space="preserve">Bronzealdervej 8</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2826,20 +2826,20 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">7349419</t>
+          <t xml:space="preserve">100052507</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J38">
-        <v>11918</v>
+        <v>324</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t xml:space="preserve">311230441</t>
+          <t xml:space="preserve">311258869</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-24</t>
+          <t xml:space="preserve">2027-07-04</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vennelundsvej 95</t>
+          <t xml:space="preserve">Rådhusgade 38</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">8375804</t>
+          <t xml:space="preserve">4196668</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2910,11 +2910,11 @@
         </is>
       </c>
       <c r="J39">
-        <v>994</v>
+        <v>1377</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t xml:space="preserve">311242492</t>
+          <t xml:space="preserve">311259724</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-24</t>
+          <t xml:space="preserve">2027-07-07</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vennelundsvej 95</t>
+          <t xml:space="preserve">Rådhusgade 43</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2976,20 +2976,20 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">8375804</t>
+          <t xml:space="preserve">4196792</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J40">
-        <v>1212</v>
+        <v>1063</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t xml:space="preserve">311242492</t>
+          <t xml:space="preserve">311259573</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2999,7 +2999,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-24</t>
+          <t xml:space="preserve">2027-07-07</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vennelundsvej 95</t>
+          <t xml:space="preserve">Rådhusgade 43</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -3051,20 +3051,20 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">8375804</t>
+          <t xml:space="preserve">4196792</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J41">
-        <v>1546</v>
+        <v>1468</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t xml:space="preserve">311242492</t>
+          <t xml:space="preserve">311259573</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3074,7 +3074,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-24</t>
+          <t xml:space="preserve">2027-07-07</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mejerivej 14</t>
+          <t xml:space="preserve">Aaholmsgade 3A</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -3126,20 +3126,20 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">4196620</t>
+          <t xml:space="preserve">4196607</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J42">
-        <v>887</v>
+        <v>301</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t xml:space="preserve">311253199</t>
+          <t xml:space="preserve">311270275</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-12</t>
+          <t xml:space="preserve">2027-09-01</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bronzealdervej 10</t>
+          <t xml:space="preserve">Aaholmsgade 3E</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">100052507</t>
+          <t xml:space="preserve">4196607</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3210,11 +3210,11 @@
         </is>
       </c>
       <c r="J43">
-        <v>787</v>
+        <v>310</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258871</t>
+          <t xml:space="preserve">311270275</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-04</t>
+          <t xml:space="preserve">2027-09-01</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bronzealdervej 12</t>
+          <t xml:space="preserve">Ålykkecentret 5</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3276,20 +3276,20 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">100052507</t>
+          <t xml:space="preserve">4196607</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J44">
-        <v>787</v>
+        <v>3261</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258871</t>
+          <t xml:space="preserve">311270273</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-04</t>
+          <t xml:space="preserve">2027-09-01</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bronzealdervej 14</t>
+          <t xml:space="preserve">Stenslund 2</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3351,20 +3351,20 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">100052507</t>
+          <t xml:space="preserve">369803</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J45">
-        <v>787</v>
+        <v>545</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258871</t>
+          <t xml:space="preserve">311271441</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-04</t>
+          <t xml:space="preserve">2027-09-07</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bronzealdervej 2</t>
+          <t xml:space="preserve">Stenslund 7</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">100052507</t>
+          <t xml:space="preserve">8097328</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3435,11 +3435,11 @@
         </is>
       </c>
       <c r="J46">
-        <v>787</v>
+        <v>556</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258871</t>
+          <t xml:space="preserve">311275612</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-04</t>
+          <t xml:space="preserve">2027-09-28</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bronzealdervej 4</t>
+          <t xml:space="preserve">Banegårdsgade 5</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3501,20 +3501,20 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">100052507</t>
+          <t xml:space="preserve">8297681</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J47">
-        <v>787</v>
+        <v>700</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258871</t>
+          <t xml:space="preserve">311275892</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-04</t>
+          <t xml:space="preserve">2027-09-29</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bronzealdervej 6</t>
+          <t xml:space="preserve">Rosensgade 10A</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3576,20 +3576,20 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">100052507</t>
+          <t xml:space="preserve">4197085</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J48">
-        <v>787</v>
+        <v>505</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258871</t>
+          <t xml:space="preserve">311276014</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-04</t>
+          <t xml:space="preserve">2027-09-29</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3641,7 +3641,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bronzealdervej 8</t>
+          <t xml:space="preserve">Rådhusgade 3</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3651,20 +3651,20 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">100052507</t>
+          <t xml:space="preserve">4197028</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J49">
-        <v>324</v>
+        <v>6516</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258869</t>
+          <t xml:space="preserve">311275868</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-04</t>
+          <t xml:space="preserve">2027-09-29</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhusgade 38</t>
+          <t xml:space="preserve">Holsteinsgade 43</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">4196668</t>
+          <t xml:space="preserve">4199447</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3735,21 +3735,21 @@
         </is>
       </c>
       <c r="J50">
-        <v>1377</v>
+        <v>8417</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t xml:space="preserve">311259724</t>
+          <t xml:space="preserve">311287701</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-07</t>
+          <t xml:space="preserve">2027-12-07</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhusgade 43</t>
+          <t xml:space="preserve">Stenslund 6</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">4196792</t>
+          <t xml:space="preserve">8331220</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3810,21 +3810,21 @@
         </is>
       </c>
       <c r="J51">
-        <v>1063</v>
+        <v>719</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t xml:space="preserve">311259573</t>
+          <t xml:space="preserve">311447305</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">John Klysner Consult ApS</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-07</t>
+          <t xml:space="preserve">2030-07-01</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhusgade 43</t>
+          <t xml:space="preserve">Præstevænget 28</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3876,30 +3876,30 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">4196792</t>
+          <t xml:space="preserve">4196608</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J52">
-        <v>1468</v>
+        <v>1313</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t xml:space="preserve">311259573</t>
+          <t xml:space="preserve">311555233</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-07</t>
+          <t xml:space="preserve">2031-10-14</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aaholmsgade 3A</t>
+          <t xml:space="preserve">Vitaparkvej 17</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3951,20 +3951,20 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">4196607</t>
+          <t xml:space="preserve">4196608</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">30</t>
         </is>
       </c>
       <c r="J53">
-        <v>301</v>
+        <v>394</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t xml:space="preserve">311270275</t>
+          <t xml:space="preserve">311555232</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3974,7 +3974,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-01</t>
+          <t xml:space="preserve">2031-10-14</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aaholmsgade 3E</t>
+          <t xml:space="preserve">Vitaparkvej 19</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -4026,20 +4026,20 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">4196607</t>
+          <t xml:space="preserve">4196608</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J54">
-        <v>310</v>
+        <v>1496</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t xml:space="preserve">311270275</t>
+          <t xml:space="preserve">311555236</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-01</t>
+          <t xml:space="preserve">2031-10-14</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ålykkecentret 5</t>
+          <t xml:space="preserve">Vitaparkvej 6</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -4101,30 +4101,30 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">4196607</t>
+          <t xml:space="preserve">4196608</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J55">
-        <v>3261</v>
+        <v>801</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t xml:space="preserve">311270273</t>
+          <t xml:space="preserve">311555234</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-01</t>
+          <t xml:space="preserve">2031-10-14</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stenslund 2</t>
+          <t xml:space="preserve">Vitaparkvej 9</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -4176,20 +4176,20 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">369803</t>
+          <t xml:space="preserve">4196608</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J56">
-        <v>545</v>
+        <v>1592</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t xml:space="preserve">311271441</t>
+          <t xml:space="preserve">311555235</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-07</t>
+          <t xml:space="preserve">2031-10-14</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stenslund 7</t>
+          <t xml:space="preserve">Vitaparkvej 9</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -4251,20 +4251,20 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">8097328</t>
+          <t xml:space="preserve">4196608</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J57">
-        <v>556</v>
+        <v>3377</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t xml:space="preserve">311275612</t>
+          <t xml:space="preserve">311555232</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-28</t>
+          <t xml:space="preserve">2031-10-14</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Banegårdsgade 5</t>
+          <t xml:space="preserve">Vitavej 63</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -4326,20 +4326,20 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">8297681</t>
+          <t xml:space="preserve">4196608</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J58">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t xml:space="preserve">311275892</t>
+          <t xml:space="preserve">311555232</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4349,7 +4349,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-29</t>
+          <t xml:space="preserve">2031-10-14</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosensgade 10A</t>
+          <t xml:space="preserve">Vitavej 71</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -4401,20 +4401,20 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">4197085</t>
+          <t xml:space="preserve">4196608</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">28</t>
         </is>
       </c>
       <c r="J59">
-        <v>505</v>
+        <v>2608</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276014</t>
+          <t xml:space="preserve">311555232</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-29</t>
+          <t xml:space="preserve">2031-10-14</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Odder Kommune</t>
+          <t xml:space="preserve">Domi Bolig</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhusgade 3</t>
+          <t xml:space="preserve">Østergade 45F</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -4476,30 +4476,30 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">4197028</t>
+          <t xml:space="preserve">369804, 369805</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J60">
-        <v>6516</v>
+        <v>699</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t xml:space="preserve">311275868</t>
+          <t xml:space="preserve">311590170</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-29</t>
+          <t xml:space="preserve">2032-04-01</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4541,7 +4541,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holsteinsgade 43</t>
+          <t xml:space="preserve">Tofts Vænge 1</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -4551,7 +4551,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">4199447</t>
+          <t xml:space="preserve">100439978</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4560,21 +4560,21 @@
         </is>
       </c>
       <c r="J61">
-        <v>8417</v>
+        <v>1105</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t xml:space="preserve">311287701</t>
+          <t xml:space="preserve">311654677</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Dansk Boligtjek ApS</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-07</t>
+          <t xml:space="preserve">2033-01-18</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stenslund 6</t>
+          <t xml:space="preserve">Vitaparkvej 1</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">8331220</t>
+          <t xml:space="preserve">4196608</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4635,21 +4635,21 @@
         </is>
       </c>
       <c r="J62">
-        <v>719</v>
+        <v>5018</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311447305</t>
+          <t xml:space="preserve">311663627</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t xml:space="preserve">John Klysner Consult ApS</t>
+          <t xml:space="preserve">Dansk Boligtjek ApS</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-07-01</t>
+          <t xml:space="preserve">2033-03-02</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Præstevænget 28</t>
+          <t xml:space="preserve">Skolevænget 3</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -4701,30 +4701,30 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">4196608</t>
+          <t xml:space="preserve">4193843</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J63">
-        <v>1313</v>
+        <v>1056</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t xml:space="preserve">311555233</t>
+          <t xml:space="preserve">311872142</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Tæthedskompagniet ApS</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-14</t>
+          <t xml:space="preserve">2035-12-08</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vitaparkvej 17</t>
+          <t xml:space="preserve">Højmarkvej 10</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -4776,30 +4776,30 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">4196608</t>
+          <t xml:space="preserve">4197393</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">30</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J64">
-        <v>394</v>
+        <v>898</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t xml:space="preserve">311555232</t>
+          <t xml:space="preserve">311915775</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">Artelia A/S</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-14</t>
+          <t xml:space="preserve">2036-07-23</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4841,7 +4841,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vitaparkvej 19</t>
+          <t xml:space="preserve">Lundevej 35A</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -4851,30 +4851,30 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">4196608</t>
+          <t xml:space="preserve">10081243</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J65">
-        <v>1496</v>
+        <v>850</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t xml:space="preserve">311555236</t>
+          <t xml:space="preserve">311915753</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">Artelia A/S</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-14</t>
+          <t xml:space="preserve">2036-07-23</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vitaparkvej 6</t>
+          <t xml:space="preserve">Parkvej 5</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -4926,30 +4926,30 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">4196608</t>
+          <t xml:space="preserve">500006, 4198718</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J66">
-        <v>801</v>
+        <v>1568</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311555234</t>
+          <t xml:space="preserve">311915754</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Artelia A/S</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-14</t>
+          <t xml:space="preserve">2036-07-23</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vitaparkvej 9</t>
+          <t xml:space="preserve">Parkvej 5</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5001,30 +5001,30 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">4196608</t>
+          <t xml:space="preserve">500006, 4198718</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J67">
-        <v>1592</v>
+        <v>1560</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311555235</t>
+          <t xml:space="preserve">311915754</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">Artelia A/S</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-14</t>
+          <t xml:space="preserve">2036-07-23</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vitaparkvej 9</t>
+          <t xml:space="preserve">Parkvej 5</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">4196608</t>
+          <t xml:space="preserve">500006, 500007, 4198718</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -5085,21 +5085,21 @@
         </is>
       </c>
       <c r="J68">
-        <v>3377</v>
+        <v>3017</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311555232</t>
+          <t xml:space="preserve">311915754</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">Artelia A/S</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-14</t>
+          <t xml:space="preserve">2036-07-23</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vitavej 63</t>
+          <t xml:space="preserve">Parkvej 5</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5151,30 +5151,30 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">4196608</t>
+          <t xml:space="preserve">500007, 4198718</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J69">
-        <v>500</v>
+        <v>332</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311555232</t>
+          <t xml:space="preserve">311915756</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">Artelia A/S</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-14</t>
+          <t xml:space="preserve">2036-07-23</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vitavej 71</t>
+          <t xml:space="preserve">Østermarksvej 21</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -5226,30 +5226,30 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">4196608</t>
+          <t xml:space="preserve">4198344</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">28</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J70">
-        <v>2608</v>
+        <v>569</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311555232</t>
+          <t xml:space="preserve">311915750</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">Artelia A/S</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-14</t>
+          <t xml:space="preserve">2036-07-23</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5276,12 +5276,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Domi Bolig</t>
+          <t xml:space="preserve">Odder Kommune</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 45F</t>
+          <t xml:space="preserve">Østermarksvej 21B</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -5301,30 +5301,30 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">369804, 369805</t>
+          <t xml:space="preserve">4198348</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J71">
-        <v>699</v>
+        <v>555</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311590170</t>
+          <t xml:space="preserve">311915749</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">Artelia A/S</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-01</t>
+          <t xml:space="preserve">2036-07-23</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tofts Vænge 1</t>
+          <t xml:space="preserve">Havrevænget 15</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -5376,7 +5376,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">100439978</t>
+          <t xml:space="preserve">8037533</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -5385,21 +5385,21 @@
         </is>
       </c>
       <c r="J72">
-        <v>1105</v>
+        <v>327</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311654677</t>
+          <t xml:space="preserve">311924130</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dansk Boligtjek ApS</t>
+          <t xml:space="preserve">Artelia A/S</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-18</t>
+          <t xml:space="preserve">2036-09-07</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5441,40 +5441,40 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vitaparkvej 1</t>
+          <t xml:space="preserve">Solhøjvej 12</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">8300</t>
+          <t xml:space="preserve">8350</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">4196608</t>
+          <t xml:space="preserve">4195321</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J73">
-        <v>5018</v>
+        <v>371</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311663627</t>
+          <t xml:space="preserve">311924150</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dansk Boligtjek ApS</t>
+          <t xml:space="preserve">Artelia A/S</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-02</t>
+          <t xml:space="preserve">2036-09-07</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevænget 3</t>
+          <t xml:space="preserve">Skolevænget 1</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -5531,25 +5531,25 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J74">
-        <v>1056</v>
+        <v>3079</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311872142</t>
+          <t xml:space="preserve">311926891</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tæthedskompagniet ApS</t>
+          <t xml:space="preserve">Artelia A/S</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-08</t>
+          <t xml:space="preserve">2036-09-19</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højmarkvej 10</t>
+          <t xml:space="preserve">Skolevænget 1</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -5601,20 +5601,20 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">4197393</t>
+          <t xml:space="preserve">4193843</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J75">
-        <v>898</v>
+        <v>695</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311915775</t>
+          <t xml:space="preserve">311926891</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-23</t>
+          <t xml:space="preserve">2036-09-19</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundevej 35A</t>
+          <t xml:space="preserve">Gylling Skolegade 13</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">10081243</t>
+          <t xml:space="preserve">4193434</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5685,11 +5685,11 @@
         </is>
       </c>
       <c r="J76">
-        <v>850</v>
+        <v>2202</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311915753</t>
+          <t xml:space="preserve">311928512</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5699,7 +5699,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-23</t>
+          <t xml:space="preserve">2036-09-28</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkvej 5</t>
+          <t xml:space="preserve">Vennelundsvej 95</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -5751,20 +5751,20 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">500006, 4198718</t>
+          <t xml:space="preserve">8375804</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J77">
-        <v>1568</v>
+        <v>994</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311915754</t>
+          <t xml:space="preserve">311928518</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-23</t>
+          <t xml:space="preserve">2036-09-28</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkvej 5</t>
+          <t xml:space="preserve">Vennelundsvej 95</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -5826,20 +5826,20 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">500006, 4198718</t>
+          <t xml:space="preserve">8375804</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J78">
-        <v>1560</v>
+        <v>1212</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311915754</t>
+          <t xml:space="preserve">311928518</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5849,7 +5849,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-23</t>
+          <t xml:space="preserve">2036-09-28</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkvej 5</t>
+          <t xml:space="preserve">Vennelundsvej 95</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -5901,20 +5901,20 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">500006, 500007, 4198718</t>
+          <t xml:space="preserve">8375804</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J79">
-        <v>3017</v>
+        <v>994</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311915754</t>
+          <t xml:space="preserve">311928518</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5924,7 +5924,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-23</t>
+          <t xml:space="preserve">2036-09-28</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkvej 5</t>
+          <t xml:space="preserve">Vennelundsvej 95</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -5976,20 +5976,20 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">500007, 4198718</t>
+          <t xml:space="preserve">8375804</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J80">
-        <v>332</v>
+        <v>1546</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311915756</t>
+          <t xml:space="preserve">311928518</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5999,7 +5999,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-23</t>
+          <t xml:space="preserve">2036-09-28</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østermarksvej 21</t>
+          <t xml:space="preserve">Vennelundsvej 95</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -6051,20 +6051,20 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">4198344</t>
+          <t xml:space="preserve">8375804</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J81">
-        <v>569</v>
+        <v>2372</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311915750</t>
+          <t xml:space="preserve">311928518</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-23</t>
+          <t xml:space="preserve">2036-09-28</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østermarksvej 21B</t>
+          <t xml:space="preserve">Alrøvej 357</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">4198348</t>
+          <t xml:space="preserve">4191418</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -6135,11 +6135,11 @@
         </is>
       </c>
       <c r="J82">
-        <v>555</v>
+        <v>417</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311915749</t>
+          <t xml:space="preserve">311929017</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -6149,7 +6149,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-23</t>
+          <t xml:space="preserve">2036-09-30</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havrevænget 15</t>
+          <t xml:space="preserve">Gylling Skolegade 12</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">8037533</t>
+          <t xml:space="preserve">4193329</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -6210,11 +6210,11 @@
         </is>
       </c>
       <c r="J83">
-        <v>327</v>
+        <v>442</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311924130</t>
+          <t xml:space="preserve">311929154</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -6224,7 +6224,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-07</t>
+          <t xml:space="preserve">2036-09-30</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -6266,30 +6266,30 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solhøjvej 12</t>
+          <t xml:space="preserve">Aahavevej 10</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">8350</t>
+          <t xml:space="preserve">8300</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">4195321</t>
+          <t xml:space="preserve">4197460</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J84">
-        <v>371</v>
+        <v>253</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311924150</t>
+          <t xml:space="preserve">311929294</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -6299,7 +6299,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-07</t>
+          <t xml:space="preserve">2036-10-01</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">

--- a/public/exports-with-coowners/32264328.xlsx
+++ b/public/exports-with-coowners/32264328.xlsx
@@ -791,26 +791,26 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tunø Hovedgade 10</t>
+          <t xml:space="preserve">Vitavej 60</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">8799</t>
+          <t xml:space="preserve">8300</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4248229</t>
+          <t xml:space="preserve">4196608</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J11">
-        <v>421</v>
+        <v>629</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vitavej 60</t>
+          <t xml:space="preserve">Holsteinsgade 43A</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -876,35 +876,35 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">4196608</t>
+          <t xml:space="preserve">4199447</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J12">
-        <v>629</v>
+        <v>759</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200026991</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Rambøll Danmark A/S (Ålborg)</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2020-01-19</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holsteinsgade 43A</t>
+          <t xml:space="preserve">Egholmvej 2</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -951,30 +951,30 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">4199447</t>
+          <t xml:space="preserve">4197672</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J13">
-        <v>759</v>
+        <v>512</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t xml:space="preserve">200026991</t>
+          <t xml:space="preserve">311203242</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S (Ålborg)</t>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-01-19</t>
+          <t xml:space="preserve">2026-09-28</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1016,7 +1016,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egholmvej 2</t>
+          <t xml:space="preserve">Bronzealdervej 16</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1026,20 +1026,20 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">4197672</t>
+          <t xml:space="preserve">4197674</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J14">
-        <v>512</v>
+        <v>270</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t xml:space="preserve">311203242</t>
+          <t xml:space="preserve">311208182</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1049,17 +1049,17 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-28</t>
+          <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egholmvej 6</t>
+          <t xml:space="preserve">Saloparken 2</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">4197674</t>
+          <t xml:space="preserve">7255382</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1110,11 +1110,11 @@
         </is>
       </c>
       <c r="J15">
-        <v>276</v>
+        <v>555</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t xml:space="preserve">311203232</t>
+          <t xml:space="preserve">311208186</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1124,17 +1124,17 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-28</t>
+          <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egholmvej 6</t>
+          <t xml:space="preserve">Skolegade 15A</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1176,20 +1176,20 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">4197674</t>
+          <t xml:space="preserve">4193708</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J16">
-        <v>282</v>
+        <v>398</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t xml:space="preserve">311203232</t>
+          <t xml:space="preserve">311218214</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-28</t>
+          <t xml:space="preserve">2026-12-16</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -1241,30 +1241,30 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egholmvej 6</t>
+          <t xml:space="preserve">Landevejen 30</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">8300</t>
+          <t xml:space="preserve">8350</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">4197674</t>
+          <t xml:space="preserve">4194779</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J17">
-        <v>294</v>
+        <v>275</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t xml:space="preserve">311203232</t>
+          <t xml:space="preserve">311221278</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1274,17 +1274,17 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-28</t>
+          <t xml:space="preserve">2027-01-06</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egholmvej 6</t>
+          <t xml:space="preserve">Rudevej 100</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1326,20 +1326,20 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">4197674</t>
+          <t xml:space="preserve">9995805</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J18">
-        <v>499</v>
+        <v>894</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t xml:space="preserve">311203232</t>
+          <t xml:space="preserve">311221240</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1349,17 +1349,17 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-28</t>
+          <t xml:space="preserve">2027-01-06</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bronzealdervej 16</t>
+          <t xml:space="preserve">Rudevej 100</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1401,20 +1401,20 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">4197674</t>
+          <t xml:space="preserve">9995805</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J19">
-        <v>270</v>
+        <v>329</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t xml:space="preserve">311208182</t>
+          <t xml:space="preserve">311221242</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-24</t>
+          <t xml:space="preserve">2027-01-06</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Saloparken 2</t>
+          <t xml:space="preserve">Rudevej 100</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1476,20 +1476,20 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">7255382</t>
+          <t xml:space="preserve">9995805</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J20">
-        <v>555</v>
+        <v>428</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t xml:space="preserve">311208186</t>
+          <t xml:space="preserve">311221240</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-24</t>
+          <t xml:space="preserve">2027-01-06</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Torvald Køhlsvej 50</t>
+          <t xml:space="preserve">Rudevej 100</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1551,20 +1551,20 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">9665232</t>
+          <t xml:space="preserve">9995805</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J21">
-        <v>398</v>
+        <v>1621</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t xml:space="preserve">311208185</t>
+          <t xml:space="preserve">311221240</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-24</t>
+          <t xml:space="preserve">2027-01-06</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 15A</t>
+          <t xml:space="preserve">Østermarksvej 25A</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">4193708</t>
+          <t xml:space="preserve">100049247</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1635,21 +1635,21 @@
         </is>
       </c>
       <c r="J22">
-        <v>398</v>
+        <v>620</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t xml:space="preserve">311218214</t>
+          <t xml:space="preserve">311224995</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">Bornak Arkitekter</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-16</t>
+          <t xml:space="preserve">2027-01-27</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Venneslaparken 1</t>
+          <t xml:space="preserve">Nølevvej 4</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">7956622</t>
+          <t xml:space="preserve">7349419</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1710,11 +1710,11 @@
         </is>
       </c>
       <c r="J23">
-        <v>480</v>
+        <v>11918</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t xml:space="preserve">311218471</t>
+          <t xml:space="preserve">311230441</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-19</t>
+          <t xml:space="preserve">2027-02-24</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -1766,30 +1766,30 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Landevejen 30</t>
+          <t xml:space="preserve">Bronzealdervej 10</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">8350</t>
+          <t xml:space="preserve">8300</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">4194779</t>
+          <t xml:space="preserve">100052507</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J24">
-        <v>275</v>
+        <v>787</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t xml:space="preserve">311221278</t>
+          <t xml:space="preserve">311258871</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-06</t>
+          <t xml:space="preserve">2027-07-04</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rudevej 100</t>
+          <t xml:space="preserve">Bronzealdervej 12</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1851,20 +1851,20 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">9995805</t>
+          <t xml:space="preserve">100052507</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J25">
-        <v>894</v>
+        <v>787</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t xml:space="preserve">311221242</t>
+          <t xml:space="preserve">311258871</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-06</t>
+          <t xml:space="preserve">2027-07-04</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -1916,7 +1916,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rudevej 100</t>
+          <t xml:space="preserve">Bronzealdervej 14</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1926,20 +1926,20 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">9995805</t>
+          <t xml:space="preserve">100052507</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J26">
-        <v>329</v>
+        <v>787</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t xml:space="preserve">311221242</t>
+          <t xml:space="preserve">311258871</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-06</t>
+          <t xml:space="preserve">2027-07-04</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rudevej 100</t>
+          <t xml:space="preserve">Bronzealdervej 2</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2001,20 +2001,20 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">9995805</t>
+          <t xml:space="preserve">100052507</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J27">
-        <v>428</v>
+        <v>787</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t xml:space="preserve">311221242</t>
+          <t xml:space="preserve">311258871</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-06</t>
+          <t xml:space="preserve">2027-07-04</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rudevej 100</t>
+          <t xml:space="preserve">Bronzealdervej 4</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2076,20 +2076,20 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">9995805</t>
+          <t xml:space="preserve">100052507</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J28">
-        <v>1621</v>
+        <v>787</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t xml:space="preserve">311221242</t>
+          <t xml:space="preserve">311258871</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-06</t>
+          <t xml:space="preserve">2027-07-04</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østermarksvej 25A</t>
+          <t xml:space="preserve">Bronzealdervej 6</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2151,30 +2151,30 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">100049247</t>
+          <t xml:space="preserve">100052507</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J29">
-        <v>620</v>
+        <v>787</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t xml:space="preserve">311224995</t>
+          <t xml:space="preserve">311258871</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bornak Arkitekter</t>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-27</t>
+          <t xml:space="preserve">2027-07-04</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nølevvej 4</t>
+          <t xml:space="preserve">Bronzealdervej 8</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2226,20 +2226,20 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">7349419</t>
+          <t xml:space="preserve">100052507</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J30">
-        <v>11918</v>
+        <v>324</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t xml:space="preserve">311230441</t>
+          <t xml:space="preserve">311258869</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-24</t>
+          <t xml:space="preserve">2027-07-04</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mejerivej 14</t>
+          <t xml:space="preserve">Rådhusgade 38</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">4196620</t>
+          <t xml:space="preserve">4196668</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2310,11 +2310,11 @@
         </is>
       </c>
       <c r="J31">
-        <v>887</v>
+        <v>1377</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t xml:space="preserve">311253199</t>
+          <t xml:space="preserve">311259724</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-12</t>
+          <t xml:space="preserve">2027-07-07</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bronzealdervej 10</t>
+          <t xml:space="preserve">Rådhusgade 43</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2376,20 +2376,20 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">100052507</t>
+          <t xml:space="preserve">4196792</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J32">
-        <v>787</v>
+        <v>1063</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258871</t>
+          <t xml:space="preserve">311259573</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2399,7 +2399,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-04</t>
+          <t xml:space="preserve">2027-07-07</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bronzealdervej 12</t>
+          <t xml:space="preserve">Rådhusgade 43</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2451,20 +2451,20 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">100052507</t>
+          <t xml:space="preserve">4196792</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J33">
-        <v>787</v>
+        <v>1468</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258871</t>
+          <t xml:space="preserve">311259573</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-04</t>
+          <t xml:space="preserve">2027-07-07</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bronzealdervej 14</t>
+          <t xml:space="preserve">Aaholmsgade 3A</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2526,20 +2526,20 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">100052507</t>
+          <t xml:space="preserve">4196607</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J34">
-        <v>787</v>
+        <v>301</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258871</t>
+          <t xml:space="preserve">311270275</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-04</t>
+          <t xml:space="preserve">2027-09-01</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bronzealdervej 2</t>
+          <t xml:space="preserve">Aaholmsgade 3E</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2601,20 +2601,20 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">100052507</t>
+          <t xml:space="preserve">4196607</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J35">
-        <v>787</v>
+        <v>310</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258871</t>
+          <t xml:space="preserve">311270275</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-04</t>
+          <t xml:space="preserve">2027-09-01</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bronzealdervej 4</t>
+          <t xml:space="preserve">Ålykkecentret 5</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2676,20 +2676,20 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">100052507</t>
+          <t xml:space="preserve">4196607</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J36">
-        <v>787</v>
+        <v>3261</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258871</t>
+          <t xml:space="preserve">311270273</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-04</t>
+          <t xml:space="preserve">2027-09-01</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bronzealdervej 6</t>
+          <t xml:space="preserve">Stenslund 2</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2751,20 +2751,20 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">100052507</t>
+          <t xml:space="preserve">369803</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J37">
-        <v>787</v>
+        <v>545</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258871</t>
+          <t xml:space="preserve">311271441</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-04</t>
+          <t xml:space="preserve">2027-09-07</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bronzealdervej 8</t>
+          <t xml:space="preserve">Stenslund 7</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2826,20 +2826,20 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">100052507</t>
+          <t xml:space="preserve">8097328</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J38">
-        <v>324</v>
+        <v>556</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258869</t>
+          <t xml:space="preserve">311275612</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-04</t>
+          <t xml:space="preserve">2027-09-28</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhusgade 38</t>
+          <t xml:space="preserve">Banegårdsgade 5</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">4196668</t>
+          <t xml:space="preserve">8297681</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2910,11 +2910,11 @@
         </is>
       </c>
       <c r="J39">
-        <v>1377</v>
+        <v>700</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t xml:space="preserve">311259724</t>
+          <t xml:space="preserve">311275892</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-07</t>
+          <t xml:space="preserve">2027-09-29</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhusgade 43</t>
+          <t xml:space="preserve">Rosensgade 10A</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">4196792</t>
+          <t xml:space="preserve">4197085</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2985,11 +2985,11 @@
         </is>
       </c>
       <c r="J40">
-        <v>1063</v>
+        <v>505</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t xml:space="preserve">311259573</t>
+          <t xml:space="preserve">311276014</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2999,7 +2999,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-07</t>
+          <t xml:space="preserve">2027-09-29</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhusgade 43</t>
+          <t xml:space="preserve">Rådhusgade 3</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -3051,20 +3051,20 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">4196792</t>
+          <t xml:space="preserve">4197028</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J41">
-        <v>1468</v>
+        <v>6516</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t xml:space="preserve">311259573</t>
+          <t xml:space="preserve">311275868</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3074,7 +3074,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-07</t>
+          <t xml:space="preserve">2027-09-29</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aaholmsgade 3A</t>
+          <t xml:space="preserve">Holsteinsgade 43</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -3126,30 +3126,30 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">4196607</t>
+          <t xml:space="preserve">4199447</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J42">
-        <v>301</v>
+        <v>8417</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t xml:space="preserve">311270275</t>
+          <t xml:space="preserve">311287701</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-01</t>
+          <t xml:space="preserve">2027-12-07</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aaholmsgade 3E</t>
+          <t xml:space="preserve">Stenslund 6</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3201,30 +3201,30 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">4196607</t>
+          <t xml:space="preserve">8331220</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J43">
-        <v>310</v>
+        <v>719</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t xml:space="preserve">311270275</t>
+          <t xml:space="preserve">311447305</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">John Klysner Consult ApS</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-01</t>
+          <t xml:space="preserve">2030-07-01</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ålykkecentret 5</t>
+          <t xml:space="preserve">Præstevænget 28</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3276,30 +3276,30 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">4196607</t>
+          <t xml:space="preserve">4196608</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J44">
-        <v>3261</v>
+        <v>1313</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t xml:space="preserve">311270273</t>
+          <t xml:space="preserve">311555233</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-01</t>
+          <t xml:space="preserve">2031-10-14</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stenslund 2</t>
+          <t xml:space="preserve">Vitaparkvej 17</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3351,20 +3351,20 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">369803</t>
+          <t xml:space="preserve">4196608</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">30</t>
         </is>
       </c>
       <c r="J45">
-        <v>545</v>
+        <v>394</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t xml:space="preserve">311271441</t>
+          <t xml:space="preserve">311555232</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-07</t>
+          <t xml:space="preserve">2031-10-14</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stenslund 7</t>
+          <t xml:space="preserve">Vitaparkvej 19</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3426,20 +3426,20 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">8097328</t>
+          <t xml:space="preserve">4196608</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J46">
-        <v>556</v>
+        <v>1496</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t xml:space="preserve">311275612</t>
+          <t xml:space="preserve">311555236</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-28</t>
+          <t xml:space="preserve">2031-10-14</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Banegårdsgade 5</t>
+          <t xml:space="preserve">Vitaparkvej 6</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3501,30 +3501,30 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">8297681</t>
+          <t xml:space="preserve">4196608</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J47">
-        <v>700</v>
+        <v>801</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t xml:space="preserve">311275892</t>
+          <t xml:space="preserve">311555234</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-29</t>
+          <t xml:space="preserve">2031-10-14</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosensgade 10A</t>
+          <t xml:space="preserve">Vitaparkvej 9</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3576,20 +3576,20 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">4197085</t>
+          <t xml:space="preserve">4196608</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J48">
-        <v>505</v>
+        <v>1592</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276014</t>
+          <t xml:space="preserve">311555235</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-29</t>
+          <t xml:space="preserve">2031-10-14</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3641,7 +3641,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhusgade 3</t>
+          <t xml:space="preserve">Vitaparkvej 9</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3651,20 +3651,20 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">4197028</t>
+          <t xml:space="preserve">4196608</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J49">
-        <v>6516</v>
+        <v>3377</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t xml:space="preserve">311275868</t>
+          <t xml:space="preserve">311555232</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-29</t>
+          <t xml:space="preserve">2031-10-14</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holsteinsgade 43</t>
+          <t xml:space="preserve">Vitavej 63</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3726,30 +3726,30 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">4199447</t>
+          <t xml:space="preserve">4196608</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J50">
-        <v>8417</v>
+        <v>500</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t xml:space="preserve">311287701</t>
+          <t xml:space="preserve">311555232</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-07</t>
+          <t xml:space="preserve">2031-10-14</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stenslund 6</t>
+          <t xml:space="preserve">Vitavej 71</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3801,30 +3801,30 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">8331220</t>
+          <t xml:space="preserve">4196608</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">28</t>
         </is>
       </c>
       <c r="J51">
-        <v>719</v>
+        <v>2608</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t xml:space="preserve">311447305</t>
+          <t xml:space="preserve">311555232</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t xml:space="preserve">John Klysner Consult ApS</t>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-07-01</t>
+          <t xml:space="preserve">2031-10-14</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Odder Kommune</t>
+          <t xml:space="preserve">Domi Bolig</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Præstevænget 28</t>
+          <t xml:space="preserve">Østergade 45F</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3876,30 +3876,30 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">4196608</t>
+          <t xml:space="preserve">369804, 369805</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J52">
-        <v>1313</v>
+        <v>699</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t xml:space="preserve">311555233</t>
+          <t xml:space="preserve">311590170</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-14</t>
+          <t xml:space="preserve">2032-04-01</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vitaparkvej 17</t>
+          <t xml:space="preserve">Tofts Vænge 1</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3951,30 +3951,30 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">4196608</t>
+          <t xml:space="preserve">100439978</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">30</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J53">
-        <v>394</v>
+        <v>1105</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t xml:space="preserve">311555232</t>
+          <t xml:space="preserve">311654677</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">Dansk Boligtjek ApS</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-14</t>
+          <t xml:space="preserve">2033-01-18</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vitaparkvej 19</t>
+          <t xml:space="preserve">Vitaparkvej 1</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -4031,25 +4031,25 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J54">
-        <v>1496</v>
+        <v>5018</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t xml:space="preserve">311555236</t>
+          <t xml:space="preserve">311663627</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">Dansk Boligtjek ApS</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-14</t>
+          <t xml:space="preserve">2033-03-02</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vitaparkvej 6</t>
+          <t xml:space="preserve">Skolevænget 3</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -4101,30 +4101,30 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">4196608</t>
+          <t xml:space="preserve">4193843</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J55">
-        <v>801</v>
+        <v>1056</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t xml:space="preserve">311555234</t>
+          <t xml:space="preserve">311872142</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Tæthedskompagniet ApS</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-14</t>
+          <t xml:space="preserve">2035-12-08</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vitaparkvej 9</t>
+          <t xml:space="preserve">Højmarkvej 10</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -4176,30 +4176,30 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">4196608</t>
+          <t xml:space="preserve">4197393</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J56">
-        <v>1592</v>
+        <v>898</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t xml:space="preserve">311555235</t>
+          <t xml:space="preserve">311915775</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">Artelia A/S</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-14</t>
+          <t xml:space="preserve">2036-07-23</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vitaparkvej 9</t>
+          <t xml:space="preserve">Lundevej 35A</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -4251,30 +4251,30 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">4196608</t>
+          <t xml:space="preserve">10081243</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J57">
-        <v>3377</v>
+        <v>850</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t xml:space="preserve">311555232</t>
+          <t xml:space="preserve">311915753</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">Artelia A/S</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-14</t>
+          <t xml:space="preserve">2036-07-23</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vitavej 63</t>
+          <t xml:space="preserve">Parkvej 5</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -4326,30 +4326,30 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">4196608</t>
+          <t xml:space="preserve">500006, 4198718</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J58">
-        <v>500</v>
+        <v>1568</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t xml:space="preserve">311555232</t>
+          <t xml:space="preserve">311915754</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">Artelia A/S</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-14</t>
+          <t xml:space="preserve">2036-07-23</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vitavej 71</t>
+          <t xml:space="preserve">Parkvej 5</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -4401,30 +4401,30 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">4196608</t>
+          <t xml:space="preserve">500006, 4198718</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">28</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J59">
-        <v>2608</v>
+        <v>1560</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t xml:space="preserve">311555232</t>
+          <t xml:space="preserve">311915754</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">Artelia A/S</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-14</t>
+          <t xml:space="preserve">2036-07-23</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Domi Bolig</t>
+          <t xml:space="preserve">Odder Kommune</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 45F</t>
+          <t xml:space="preserve">Parkvej 5</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -4476,30 +4476,30 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">369804, 369805</t>
+          <t xml:space="preserve">500006, 500007, 4198718</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J60">
-        <v>699</v>
+        <v>3017</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t xml:space="preserve">311590170</t>
+          <t xml:space="preserve">311915754</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">Artelia A/S</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-01</t>
+          <t xml:space="preserve">2036-07-23</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4541,7 +4541,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tofts Vænge 1</t>
+          <t xml:space="preserve">Parkvej 5</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -4551,30 +4551,30 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">100439978</t>
+          <t xml:space="preserve">500007, 4198718</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J61">
-        <v>1105</v>
+        <v>332</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t xml:space="preserve">311654677</t>
+          <t xml:space="preserve">311915756</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dansk Boligtjek ApS</t>
+          <t xml:space="preserve">Artelia A/S</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-18</t>
+          <t xml:space="preserve">2036-07-23</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vitaparkvej 1</t>
+          <t xml:space="preserve">Østermarksvej 21</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">4196608</t>
+          <t xml:space="preserve">4198344</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4635,21 +4635,21 @@
         </is>
       </c>
       <c r="J62">
-        <v>5018</v>
+        <v>569</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311663627</t>
+          <t xml:space="preserve">311915750</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dansk Boligtjek ApS</t>
+          <t xml:space="preserve">Artelia A/S</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-02</t>
+          <t xml:space="preserve">2036-07-23</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevænget 3</t>
+          <t xml:space="preserve">Østermarksvej 21B</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -4701,30 +4701,30 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">4193843</t>
+          <t xml:space="preserve">4198348</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J63">
-        <v>1056</v>
+        <v>555</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t xml:space="preserve">311872142</t>
+          <t xml:space="preserve">311915749</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tæthedskompagniet ApS</t>
+          <t xml:space="preserve">Artelia A/S</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-08</t>
+          <t xml:space="preserve">2036-07-23</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højmarkvej 10</t>
+          <t xml:space="preserve">Havrevænget 15</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">4197393</t>
+          <t xml:space="preserve">8037533</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4785,11 +4785,11 @@
         </is>
       </c>
       <c r="J64">
-        <v>898</v>
+        <v>327</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t xml:space="preserve">311915775</t>
+          <t xml:space="preserve">311924130</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-23</t>
+          <t xml:space="preserve">2036-09-07</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4841,30 +4841,30 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundevej 35A</t>
+          <t xml:space="preserve">Solhøjvej 12</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">8300</t>
+          <t xml:space="preserve">8350</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">10081243</t>
+          <t xml:space="preserve">4195321</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J65">
-        <v>850</v>
+        <v>371</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t xml:space="preserve">311915753</t>
+          <t xml:space="preserve">311924150</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4874,7 +4874,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-23</t>
+          <t xml:space="preserve">2036-09-07</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkvej 5</t>
+          <t xml:space="preserve">Skolevænget 1</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -4926,20 +4926,20 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">500006, 4198718</t>
+          <t xml:space="preserve">4193843</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J66">
-        <v>1568</v>
+        <v>3079</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311915754</t>
+          <t xml:space="preserve">311926891</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-23</t>
+          <t xml:space="preserve">2036-09-19</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkvej 5</t>
+          <t xml:space="preserve">Skolevænget 1</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5001,20 +5001,20 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">500006, 4198718</t>
+          <t xml:space="preserve">4193843</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J67">
-        <v>1560</v>
+        <v>695</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311915754</t>
+          <t xml:space="preserve">311926891</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-23</t>
+          <t xml:space="preserve">2036-09-19</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkvej 5</t>
+          <t xml:space="preserve">Gylling Skolegade 13</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5076,20 +5076,20 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">500006, 500007, 4198718</t>
+          <t xml:space="preserve">4193434</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J68">
-        <v>3017</v>
+        <v>2202</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311915754</t>
+          <t xml:space="preserve">311928512</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-23</t>
+          <t xml:space="preserve">2036-09-28</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkvej 5</t>
+          <t xml:space="preserve">Vennelundsvej 95</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5151,20 +5151,20 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">500007, 4198718</t>
+          <t xml:space="preserve">8375804</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J69">
-        <v>332</v>
+        <v>994</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311915756</t>
+          <t xml:space="preserve">311928518</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-23</t>
+          <t xml:space="preserve">2036-09-28</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østermarksvej 21</t>
+          <t xml:space="preserve">Vennelundsvej 95</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -5226,20 +5226,20 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">4198344</t>
+          <t xml:space="preserve">8375804</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J70">
-        <v>569</v>
+        <v>1212</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311915750</t>
+          <t xml:space="preserve">311928518</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-23</t>
+          <t xml:space="preserve">2036-09-28</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østermarksvej 21B</t>
+          <t xml:space="preserve">Vennelundsvej 95</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -5301,20 +5301,20 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">4198348</t>
+          <t xml:space="preserve">8375804</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J71">
-        <v>555</v>
+        <v>994</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311915749</t>
+          <t xml:space="preserve">311928518</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-23</t>
+          <t xml:space="preserve">2036-09-28</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havrevænget 15</t>
+          <t xml:space="preserve">Vennelundsvej 95</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -5376,20 +5376,20 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">8037533</t>
+          <t xml:space="preserve">8375804</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J72">
-        <v>327</v>
+        <v>1546</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311924130</t>
+          <t xml:space="preserve">311928518</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-07</t>
+          <t xml:space="preserve">2036-09-28</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5441,30 +5441,30 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solhøjvej 12</t>
+          <t xml:space="preserve">Vennelundsvej 95</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">8350</t>
+          <t xml:space="preserve">8300</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">4195321</t>
+          <t xml:space="preserve">8375804</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J73">
-        <v>371</v>
+        <v>2372</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311924150</t>
+          <t xml:space="preserve">311928518</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-07</t>
+          <t xml:space="preserve">2036-09-28</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevænget 1</t>
+          <t xml:space="preserve">Alrøvej 357</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">4193843</t>
+          <t xml:space="preserve">4191418</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5535,11 +5535,11 @@
         </is>
       </c>
       <c r="J74">
-        <v>3079</v>
+        <v>417</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311926891</t>
+          <t xml:space="preserve">311929017</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-19</t>
+          <t xml:space="preserve">2036-09-30</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevænget 1</t>
+          <t xml:space="preserve">Gylling Skolegade 12</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -5601,20 +5601,20 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">4193843</t>
+          <t xml:space="preserve">4193329</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J75">
-        <v>695</v>
+        <v>442</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311926891</t>
+          <t xml:space="preserve">311929154</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-19</t>
+          <t xml:space="preserve">2036-09-30</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gylling Skolegade 13</t>
+          <t xml:space="preserve">Aahavevej 10</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">4193434</t>
+          <t xml:space="preserve">4197460</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5685,11 +5685,11 @@
         </is>
       </c>
       <c r="J76">
-        <v>2202</v>
+        <v>253</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311928512</t>
+          <t xml:space="preserve">311929675</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5699,7 +5699,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-28</t>
+          <t xml:space="preserve">2036-10-01</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vennelundsvej 95</t>
+          <t xml:space="preserve">Venneslaparken 1</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -5751,7 +5751,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">8375804</t>
+          <t xml:space="preserve">7956622</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5760,11 +5760,11 @@
         </is>
       </c>
       <c r="J77">
-        <v>994</v>
+        <v>480</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311928518</t>
+          <t xml:space="preserve">311929537</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-28</t>
+          <t xml:space="preserve">2036-10-02</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vennelundsvej 95</t>
+          <t xml:space="preserve">Mejerivej 14</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -5826,20 +5826,20 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">8375804</t>
+          <t xml:space="preserve">4196620</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J78">
-        <v>1212</v>
+        <v>887</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311928518</t>
+          <t xml:space="preserve">311930179</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5849,7 +5849,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-28</t>
+          <t xml:space="preserve">2036-10-06</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vennelundsvej 95</t>
+          <t xml:space="preserve">Egholmvej 6</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -5901,20 +5901,20 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">8375804</t>
+          <t xml:space="preserve">4197674</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J79">
-        <v>994</v>
+        <v>276</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311928518</t>
+          <t xml:space="preserve">311930676</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5924,7 +5924,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-28</t>
+          <t xml:space="preserve">2036-10-08</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vennelundsvej 95</t>
+          <t xml:space="preserve">Egholmvej 6</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -5976,20 +5976,20 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">8375804</t>
+          <t xml:space="preserve">4197674</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J80">
-        <v>1546</v>
+        <v>282</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311928518</t>
+          <t xml:space="preserve">311930676</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5999,7 +5999,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-28</t>
+          <t xml:space="preserve">2036-10-08</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vennelundsvej 95</t>
+          <t xml:space="preserve">Egholmvej 6</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -6051,20 +6051,20 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">8375804</t>
+          <t xml:space="preserve">4197674</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J81">
-        <v>2372</v>
+        <v>294</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311928518</t>
+          <t xml:space="preserve">311930676</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-28</t>
+          <t xml:space="preserve">2036-10-08</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alrøvej 357</t>
+          <t xml:space="preserve">Egholmvej 6</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -6126,20 +6126,20 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">4191418</t>
+          <t xml:space="preserve">4197674</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J82">
-        <v>417</v>
+        <v>499</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311929017</t>
+          <t xml:space="preserve">311930676</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -6149,7 +6149,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-30</t>
+          <t xml:space="preserve">2036-10-08</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gylling Skolegade 12</t>
+          <t xml:space="preserve">Torvald Køhlsvej 50</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">4193329</t>
+          <t xml:space="preserve">9665232</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -6210,11 +6210,11 @@
         </is>
       </c>
       <c r="J83">
-        <v>442</v>
+        <v>398</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311929154</t>
+          <t xml:space="preserve">311930697</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -6224,7 +6224,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-30</t>
+          <t xml:space="preserve">2036-10-08</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -6266,30 +6266,30 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aahavevej 10</t>
+          <t xml:space="preserve">Tunø Hovedgade 10</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">8300</t>
+          <t xml:space="preserve">8799</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">4197460</t>
+          <t xml:space="preserve">4248229</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J84">
-        <v>253</v>
+        <v>421</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311929294</t>
+          <t xml:space="preserve">311931066</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -6299,7 +6299,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-10-01</t>
+          <t xml:space="preserve">2036-10-09</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
